--- a/planilha_dashboard_logistica.xlsx
+++ b/planilha_dashboard_logistica.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,48 +413,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID_Entrega</t>
+          <t>id_entrega</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Transportadora</t>
+          <t>transportadora</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Regiao</t>
+          <t>regiao</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Data_Prevista</t>
+          <t>prazo_dias</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Data_Entrega</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>dias_reais</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LogFast</t>
+          <t>RotaMax</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,302 +457,116 @@
           <t>Sul</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Entregue</t>
-        </is>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RapidoSul</t>
+          <t>ViaCargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sul</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46177</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Atrasada</t>
-        </is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ExpressoBR</t>
+          <t>FlashLog</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sudeste</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Entregue</t>
-        </is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1004</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LogFast</t>
+          <t>RotaMax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nordeste</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46177</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46180</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Atrasada</t>
-        </is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1005</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ExpressoBR</t>
+          <t>ViaCargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46178</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Entregue</t>
-        </is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1006</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RapidoSul</t>
+          <t>FlashLog</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Centro-Oeste</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46179</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Atrasada</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LogFast</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sudeste</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46180</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46180</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Entregue</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ExpressoBR</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>Sul</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>46181</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Atrasada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RapidoSul</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nordeste</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46182</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Entregue</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1010</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LogFast</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Norte</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Atrasada</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1011</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ExpressoBR</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sudeste</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Entregue</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1012</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RapidoSul</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sul</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Atrasada</t>
-        </is>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
